--- a/runs/ssdlite_mobilenet_27.05.20262/training_metrics.xlsx
+++ b/runs/ssdlite_mobilenet_27.05.20262/training_metrics.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1475,6 +1475,3933 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.009972699999999999</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.4857</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.2644</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.9544</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.00996698</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0.7103</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.7452</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1.4555</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.7047</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1.2737</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.9784</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0.5349</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0.5765</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.009960709999999999</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7242</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.4205</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.6732</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.2331</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1.9063</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.1547</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0.0099539</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.7064</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1.2305</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0.2917</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.00994654</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.6783</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.3663</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.9196</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.00993865</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>1.3375</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1.2438</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.9104</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0.5748</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0.5904</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0.00993022</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.5657</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0.2048</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.00992125</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>1.2952</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1.2072</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.8656</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0.5338000000000001</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.5941</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0.5598</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>0.4167</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0.00991174</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.6431</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.2724</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.6423</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.1966</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1.8389</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0.6106</v>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.009901689999999999</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.6218</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1.2607</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.6597</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.8726</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0.5542</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0.00989111</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.6062</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1.2371</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1.8358</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0.00987999</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.6231</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1.2148</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1.2138</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.8462</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0.5493</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.00986834</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1.1982</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.6373</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.1967</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1.8341</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>0.5647</v>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="W25" s="5" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="X25" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0.009856159999999999</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1.2172</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.8611</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0.00984345</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1.1738</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1.8078</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="U27" s="5" t="n">
+        <v>0.5883</v>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="W27" s="5" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0.009830210000000001</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>1.1548</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1.2045</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.8325</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0.5879</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0.6676</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0.009816439999999999</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.5487</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.1491</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.2339</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1.8864</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>0.6495</v>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="W29" s="5" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="X29" s="5" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.009802150000000001</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1.1349</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1.2269</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.8715</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.00978733</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.5896</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0.5272</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.1167</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1.2398</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1.8687</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="W31" s="5" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="X31" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.00977198</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1.1067</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1.1988</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0.5567</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0.00975612</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.0958</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1.2211</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1.8721</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="W33" s="5" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0.00973974</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1.0788</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1.2501</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>0.5593</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>0.6467000000000001</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.00972284</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1.0731</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>1.2622</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1.8938</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="W35" s="5" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="X35" s="5" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0.009705419999999999</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.4914</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1.0657</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.8451</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>0.5657</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.00968749</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>1.0551</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1.3109</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1.9691</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.5884</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0.00966905</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1.0454</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1.2634</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1.8884</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>0.5773</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>0.6287</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.00965009</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1.0421</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.6266</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1.3074</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0.1943</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0.2917</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.009630629999999999</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1.0303</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.6261</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1.3076</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1.9337</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.00961067</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1.0231</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.2784</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.9044</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.2132</v>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0.0095902</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1.0069</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.6421</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>0.6138</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.00956923</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1.2597</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>1.9439</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0.5598</v>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>0.6182</v>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="W43" s="5" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="X43" s="5" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0.009547760000000001</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.6182</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>1.3282</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1.9464</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>0.5943000000000001</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.009525789999999999</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.2955</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>1.9271</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.1882</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>0.6182</v>
+      </c>
+      <c r="V45" s="5" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="W45" s="5" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="X45" s="5" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0.009503330000000001</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.8958</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="Y46" s="4" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.00948038</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.2895</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>1.8961</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="S47" s="5" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="U47" s="5" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0.00945694</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.9634</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1.3185</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="R48" s="4" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>0.5961</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="X48" s="4" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="Y48" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.00943301</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1.2716</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>1.8525</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="S49" s="5" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="U49" s="5" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="V49" s="5" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="W49" s="5" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="X49" s="5" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0.0094086</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.5971</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1.3277</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1.9247</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="X50" s="4" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="Y50" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.0093837</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.6599</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1.2985</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>1.9583</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="S51" s="5" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="T51" s="5" t="n">
+        <v>0.6114000000000001</v>
+      </c>
+      <c r="U51" s="5" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="V51" s="5" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="W51" s="5" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="X51" s="5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0.00935833</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1.9273</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.3191</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>0.1392</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="Y52" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0.009332490000000001</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>1.3689</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>1.9755</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="S53" s="5" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="U53" s="5" t="n">
+        <v>0.5931999999999999</v>
+      </c>
+      <c r="V53" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="W53" s="5" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="X53" s="5" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="Y53" s="5" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0.009306170000000001</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.9323</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>1.3448</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1.9832</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>0.6044</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="Y54" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0.00927938</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1.4258</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>2.0427</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>0.5325</v>
+      </c>
+      <c r="S55" s="5" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="U55" s="5" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="V55" s="5" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="W55" s="5" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="X55" s="5" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="Y55" s="5" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>0.009252120000000001</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.9173</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>1.3328</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1.9325</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="X56" s="4" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="Y56" s="4" t="n">
+        <v>0.2917</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0.009224400000000001</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.9156</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>1.3306</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>1.9221</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="R57" s="5" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="S57" s="5" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="T57" s="5" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="U57" s="5" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="V57" s="5" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="W57" s="5" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="X57" s="5" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="Y57" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>0.00919622</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.9099</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1.4083</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>2.0209</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>0.5401</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>0.5976</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="X58" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y58" s="4" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>0.00916758</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.9009</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.6091</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>1.9426</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="R59" s="5" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="S59" s="5" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>0.5971</v>
+      </c>
+      <c r="U59" s="5" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="V59" s="5" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="W59" s="5" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="X59" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y59" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>0.009138490000000001</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>1.3426</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>1.9383</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="X60" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Y60" s="4" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>0.009108939999999999</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.8932</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="P61" s="5" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="Q61" s="5" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="R61" s="5" t="n">
+        <v>0.5329</v>
+      </c>
+      <c r="S61" s="5" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="T61" s="5" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="U61" s="5" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="V61" s="5" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="W61" s="5" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="X61" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Y61" s="5" t="n">
+        <v>0.2083</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>0.009078950000000001</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.8839</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>1.3832</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>1.9706</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="R62" s="4" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="T62" s="4" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="W62" s="4" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="X62" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y62" s="4" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>0.009048509999999999</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.8798</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>1.9813</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="Q63" s="5" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="R63" s="5" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="S63" s="5" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="T63" s="5" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="U63" s="5" t="n">
+        <v>0.6042999999999999</v>
+      </c>
+      <c r="V63" s="5" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="W63" s="5" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="X63" s="5" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="Y63" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
